--- a/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/GunnerStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/GunnerStatData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\CharData\ClassData\1. ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ClassData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401BE65F-9D7D-4221-8A29-FEEA112C93B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDD9234-9ECA-4C55-A236-30CDE5CC5326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="660" windowWidth="24450" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -436,25 +436,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.125" style="1"/>
+    <col min="3" max="3" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="1"/>
     <col min="11" max="11" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,21 +542,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="C3">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="D3">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -586,21 +586,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>470</v>
+        <v>208</v>
       </c>
       <c r="C4">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="D4">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -630,21 +630,21 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>526</v>
+        <v>216</v>
       </c>
       <c r="C5">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="D5">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -674,21 +674,21 @@
         <v>499</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>588</v>
+        <v>224</v>
       </c>
       <c r="C6">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="D6">
-        <v>210</v>
+        <v>87</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -718,21 +718,21 @@
         <v>757</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>658</v>
+        <v>232</v>
       </c>
       <c r="C7">
-        <v>275</v>
+        <v>197</v>
       </c>
       <c r="D7">
-        <v>235</v>
+        <v>92</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -762,21 +762,21 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>731</v>
+        <v>240</v>
       </c>
       <c r="C8">
-        <v>290</v>
+        <v>205</v>
       </c>
       <c r="D8">
-        <v>261</v>
+        <v>97</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -806,21 +806,21 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>818</v>
+        <v>248</v>
       </c>
       <c r="C9">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="D9">
-        <v>292</v>
+        <v>102</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>11</v>
@@ -850,21 +850,21 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>913</v>
+        <v>256</v>
       </c>
       <c r="C10">
-        <v>320</v>
+        <v>221</v>
       </c>
       <c r="D10">
-        <v>326</v>
+        <v>107</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F10">
         <v>12</v>
@@ -894,21 +894,21 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1022</v>
+        <v>264</v>
       </c>
       <c r="C11">
-        <v>335</v>
+        <v>229</v>
       </c>
       <c r="D11">
-        <v>365</v>
+        <v>112</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>13</v>
@@ -938,21 +938,21 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1142</v>
+        <v>272</v>
       </c>
       <c r="C12">
-        <v>350</v>
+        <v>237</v>
       </c>
       <c r="D12">
-        <v>408</v>
+        <v>117</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F12">
         <v>14</v>
@@ -982,21 +982,21 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1277</v>
+        <v>280</v>
       </c>
       <c r="C13">
-        <v>365</v>
+        <v>245</v>
       </c>
       <c r="D13">
-        <v>456</v>
+        <v>122</v>
       </c>
       <c r="E13">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F13">
         <v>15</v>
@@ -1026,21 +1026,21 @@
         <v>3243</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1425</v>
+        <v>288</v>
       </c>
       <c r="C14">
-        <v>380</v>
+        <v>253</v>
       </c>
       <c r="D14">
-        <v>509</v>
+        <v>127</v>
       </c>
       <c r="E14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>16</v>
@@ -1070,21 +1070,21 @@
         <v>3674</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>1593</v>
+        <v>296</v>
       </c>
       <c r="C15">
-        <v>395</v>
+        <v>261</v>
       </c>
       <c r="D15">
-        <v>569</v>
+        <v>132</v>
       </c>
       <c r="E15">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F15">
         <v>17</v>
@@ -1114,21 +1114,21 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>1781</v>
+        <v>304</v>
       </c>
       <c r="C16">
-        <v>410</v>
+        <v>269</v>
       </c>
       <c r="D16">
-        <v>636</v>
+        <v>137</v>
       </c>
       <c r="E16">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F16">
         <v>18</v>
@@ -1158,21 +1158,21 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>1991</v>
+        <v>312</v>
       </c>
       <c r="C17">
-        <v>425</v>
+        <v>277</v>
       </c>
       <c r="D17">
-        <v>711</v>
+        <v>142</v>
       </c>
       <c r="E17">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F17">
         <v>19</v>
@@ -1202,21 +1202,21 @@
         <v>5057</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>2226</v>
+        <v>320</v>
       </c>
       <c r="C18">
-        <v>440</v>
+        <v>285</v>
       </c>
       <c r="D18">
-        <v>795</v>
+        <v>147</v>
       </c>
       <c r="E18">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1246,21 +1246,21 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19">
-        <v>2486</v>
+        <v>328</v>
       </c>
       <c r="C19">
-        <v>455</v>
+        <v>293</v>
       </c>
       <c r="D19">
-        <v>888</v>
+        <v>152</v>
       </c>
       <c r="E19">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F19">
         <v>21</v>
@@ -1290,21 +1290,21 @@
         <v>6045</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20">
-        <v>2778</v>
+        <v>336</v>
       </c>
       <c r="C20">
-        <v>470</v>
+        <v>301</v>
       </c>
       <c r="D20">
-        <v>992</v>
+        <v>157</v>
       </c>
       <c r="E20">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="F20">
         <v>22</v>
@@ -1334,21 +1334,21 @@
         <v>6558</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>3105</v>
+        <v>344</v>
       </c>
       <c r="C21">
-        <v>485</v>
+        <v>309</v>
       </c>
       <c r="D21">
-        <v>1109</v>
+        <v>162</v>
       </c>
       <c r="E21">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="F21">
         <v>23</v>
@@ -1378,21 +1378,21 @@
         <v>7082</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22">
-        <v>3464</v>
+        <v>352</v>
       </c>
       <c r="C22">
-        <v>500</v>
+        <v>317</v>
       </c>
       <c r="D22">
-        <v>1237</v>
+        <v>167</v>
       </c>
       <c r="E22">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="F22">
         <v>24</v>
